--- a/backend/State of the Market Report - Nov 2023.xlsx
+++ b/backend/State of the Market Report - Nov 2023.xlsx
@@ -149,13 +149,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -499,7 +502,10 @@
   <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="6" width="9" style="1" customWidth="1"/>
+    <col min="1" max="1" width="35" style="1" customWidth="1"/>
+    <col min="2" max="3" width="12" style="1" customWidth="1"/>
+    <col min="4" max="5" width="9" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -512,24 +518,24 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="2">
@@ -538,18 +544,18 @@
       <c r="E2" s="2">
         <v>4.8</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="3">
         <v>-0.016666666666666684</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="2">
@@ -558,18 +564,18 @@
       <c r="E3" s="2">
         <v>5.33</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="2">
@@ -578,18 +584,18 @@
       <c r="E4" s="2">
         <v>310.16</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="3">
         <v>0.004320350786690659</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="2">
@@ -598,18 +604,18 @@
       <c r="E5" s="2">
         <v>3.8</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="3">
         <v>0.026315789473684237</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="2">
@@ -618,18 +624,18 @@
       <c r="E6" s="2">
         <v>306.27</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="3">
         <v>0.003950762399190376</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D7" s="2">
@@ -638,18 +644,18 @@
       <c r="E7" s="2">
         <v>18714.7</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="3">
         <v>0.007411286315035813</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="2">
@@ -658,18 +664,18 @@
       <c r="E8" s="2">
         <v>9497</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="3">
         <v>0.005896598925976624</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D9" s="2">
@@ -678,18 +684,18 @@
       <c r="E9" s="2">
         <v>3.7</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="2">
@@ -698,18 +704,18 @@
       <c r="E10" s="2">
         <v>3.6</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="3">
         <v>-0.0277777777777778</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="2">
@@ -718,18 +724,18 @@
       <c r="E11" s="2">
         <v>4</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="3">
         <v>-0.15000000000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D12" s="2">
@@ -738,7 +744,7 @@
       <c r="E12" s="2">
         <v>98</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="3">
         <v>0</v>
       </c>
     </row>
@@ -753,7 +759,8 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="9" style="1" customWidth="1"/>
+    <col min="1" max="1" width="30" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">

--- a/backend/State of the Market Report - Nov 2023.xlsx
+++ b/backend/State of the Market Report - Nov 2023.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="29">
   <si>
     <t>Indicator</t>
   </si>
@@ -35,28 +35,13 @@
     <t>Yield Curve</t>
   </si>
   <si>
-    <t>2023-11-01</t>
-  </si>
-  <si>
-    <t>2023-10-01</t>
-  </si>
-  <si>
     <t>Federal Funds Rate</t>
   </si>
   <si>
     <t>Case-Shiller Index</t>
   </si>
   <si>
-    <t>2023-08-01</t>
-  </si>
-  <si>
-    <t>2023-07-01</t>
-  </si>
-  <si>
     <t>Unemployment Rate</t>
-  </si>
-  <si>
-    <t>2023-09-01</t>
   </si>
   <si>
     <t>CPI</t>
@@ -120,6 +105,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="mmm yyyy"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
@@ -149,15 +137,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -503,248 +503,249 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" style="1" customWidth="1"/>
-    <col min="2" max="3" width="12" style="1" customWidth="1"/>
-    <col min="4" max="5" width="9" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9" style="3" customWidth="1"/>
+    <col min="2" max="2" width="12" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12" style="1" customWidth="1"/>
+    <col min="4" max="5" width="10" style="3" customWidth="1"/>
+    <col min="6" max="6" width="9" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2">
+        <v>45231</v>
+      </c>
+      <c r="C2" s="7">
+        <v>45200</v>
+      </c>
+      <c r="D2" s="3">
+        <v>4.72</v>
+      </c>
+      <c r="E2" s="3">
+        <v>4.8</v>
+      </c>
+      <c r="F2" s="4">
+        <v>-0.016666666666666684</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B3" s="2">
+        <v>45231</v>
+      </c>
+      <c r="C3" s="7">
+        <v>45200</v>
+      </c>
+      <c r="D3" s="3">
+        <v>5.33</v>
+      </c>
+      <c r="E3" s="3">
+        <v>5.33</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2">
-        <v>4.72</v>
-      </c>
-      <c r="E2" s="2">
-        <v>4.8</v>
-      </c>
-      <c r="F2" s="3">
-        <v>-0.016666666666666684</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B4" s="2">
+        <v>45139</v>
+      </c>
+      <c r="C4" s="7">
+        <v>45108</v>
+      </c>
+      <c r="D4" s="3">
+        <v>311.5</v>
+      </c>
+      <c r="E4" s="3">
+        <v>310.16</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.004320350786690659</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2">
-        <v>5.33</v>
-      </c>
-      <c r="E3" s="2">
-        <v>5.33</v>
-      </c>
-      <c r="F3" s="3">
+      <c r="B5" s="2">
+        <v>45200</v>
+      </c>
+      <c r="C5" s="7">
+        <v>45170</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3.9</v>
+      </c>
+      <c r="E5" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.026315789473684237</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2">
+        <v>45170</v>
+      </c>
+      <c r="C6" s="7">
+        <v>45139</v>
+      </c>
+      <c r="D6" s="3">
+        <v>307.48</v>
+      </c>
+      <c r="E6" s="3">
+        <v>306.27</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.003950762399190376</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2">
+        <v>45170</v>
+      </c>
+      <c r="C7" s="7">
+        <v>45139</v>
+      </c>
+      <c r="D7" s="3">
+        <v>18853.4</v>
+      </c>
+      <c r="E7" s="3">
+        <v>18714.7</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0.007411286315035813</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="2">
+        <v>45170</v>
+      </c>
+      <c r="C8" s="7">
+        <v>45139</v>
+      </c>
+      <c r="D8" s="3">
+        <v>9553</v>
+      </c>
+      <c r="E8" s="3">
+        <v>9497</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0.005896598925976624</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="2">
+        <v>45170</v>
+      </c>
+      <c r="C9" s="7">
+        <v>45139</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3.7</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3.7</v>
+      </c>
+      <c r="F9" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="2">
-        <v>311.5</v>
-      </c>
-      <c r="E4" s="2">
-        <v>310.16</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0.004320350786690659</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="1" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="2">
-        <v>3.9</v>
-      </c>
-      <c r="E5" s="2">
-        <v>3.8</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0.026315789473684237</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="B10" s="2">
+        <v>45170</v>
+      </c>
+      <c r="C10" s="7">
+        <v>45139</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="F10" s="4">
+        <v>-0.0277777777777778</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="2">
-        <v>307.48</v>
-      </c>
-      <c r="E6" s="2">
-        <v>306.27</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0.003950762399190376</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="B11" s="2">
+        <v>45170</v>
+      </c>
+      <c r="C11" s="7">
+        <v>45139</v>
+      </c>
+      <c r="D11" s="3">
+        <v>3.4</v>
+      </c>
+      <c r="E11" s="3">
+        <v>4</v>
+      </c>
+      <c r="F11" s="4">
+        <v>-0.15000000000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="2">
-        <v>18853.4</v>
-      </c>
-      <c r="E7" s="2">
-        <v>18714.7</v>
-      </c>
-      <c r="F7" s="3">
-        <v>0.007411286315035813</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="2">
-        <v>9553</v>
-      </c>
-      <c r="E8" s="2">
-        <v>9497</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0.005896598925976624</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="2">
-        <v>3.7</v>
-      </c>
-      <c r="E9" s="2">
-        <v>3.7</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="2">
-        <v>3.5</v>
-      </c>
-      <c r="E10" s="2">
-        <v>3.6</v>
-      </c>
-      <c r="F10" s="3">
-        <v>-0.0277777777777778</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="2">
-        <v>3.4</v>
-      </c>
-      <c r="E11" s="2">
-        <v>4</v>
-      </c>
-      <c r="F11" s="3">
-        <v>-0.15000000000000002</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="2">
+      <c r="B12" s="2">
+        <v>45170</v>
+      </c>
+      <c r="C12" s="7">
+        <v>45139</v>
+      </c>
+      <c r="D12" s="3">
         <v>98</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="3">
         <v>98</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="4">
         <v>0</v>
       </c>
     </row>
@@ -768,7 +769,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -776,87 +777,87 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/backend/State of the Market Report - Nov 2023.xlsx
+++ b/backend/State of the Market Report - Nov 2023.xlsx
@@ -137,10 +137,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -151,14 +151,17 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -503,29 +506,28 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12" style="1" customWidth="1"/>
+    <col min="2" max="3" width="13" style="2" customWidth="1"/>
     <col min="4" max="5" width="10" style="3" customWidth="1"/>
     <col min="6" max="6" width="9" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
     </row>
@@ -536,7 +538,7 @@
       <c r="B2" s="2">
         <v>45231</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="2">
         <v>45200</v>
       </c>
       <c r="D2" s="3">
@@ -556,7 +558,7 @@
       <c r="B3" s="2">
         <v>45231</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="2">
         <v>45200</v>
       </c>
       <c r="D3" s="3">
@@ -576,7 +578,7 @@
       <c r="B4" s="2">
         <v>45139</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="2">
         <v>45108</v>
       </c>
       <c r="D4" s="3">
@@ -596,7 +598,7 @@
       <c r="B5" s="2">
         <v>45200</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="2">
         <v>45170</v>
       </c>
       <c r="D5" s="3">
@@ -616,7 +618,7 @@
       <c r="B6" s="2">
         <v>45170</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="2">
         <v>45139</v>
       </c>
       <c r="D6" s="3">
@@ -636,7 +638,7 @@
       <c r="B7" s="2">
         <v>45170</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="2">
         <v>45139</v>
       </c>
       <c r="D7" s="3">
@@ -656,7 +658,7 @@
       <c r="B8" s="2">
         <v>45170</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="2">
         <v>45139</v>
       </c>
       <c r="D8" s="3">
@@ -676,7 +678,7 @@
       <c r="B9" s="2">
         <v>45170</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="2">
         <v>45139</v>
       </c>
       <c r="D9" s="3">
@@ -696,7 +698,7 @@
       <c r="B10" s="2">
         <v>45170</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="2">
         <v>45139</v>
       </c>
       <c r="D10" s="3">
@@ -716,7 +718,7 @@
       <c r="B11" s="2">
         <v>45170</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="2">
         <v>45139</v>
       </c>
       <c r="D11" s="3">
@@ -736,7 +738,7 @@
       <c r="B12" s="2">
         <v>45170</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="2">
         <v>45139</v>
       </c>
       <c r="D12" s="3">
@@ -761,14 +763,14 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9" style="1" customWidth="1"/>
+    <col min="2" max="2" width="100" style="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>17</v>
       </c>
     </row>
@@ -776,7 +778,7 @@
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="8" t="s">
         <v>18</v>
       </c>
     </row>
@@ -784,7 +786,7 @@
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="8" t="s">
         <v>19</v>
       </c>
     </row>
@@ -792,7 +794,7 @@
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="8" t="s">
         <v>20</v>
       </c>
     </row>
@@ -800,7 +802,7 @@
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="8" t="s">
         <v>21</v>
       </c>
     </row>
@@ -808,7 +810,7 @@
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="8" t="s">
         <v>22</v>
       </c>
     </row>
@@ -816,7 +818,7 @@
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="8" t="s">
         <v>23</v>
       </c>
     </row>
@@ -824,7 +826,7 @@
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="8" t="s">
         <v>24</v>
       </c>
     </row>
@@ -832,7 +834,7 @@
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="8" t="s">
         <v>25</v>
       </c>
     </row>
@@ -840,7 +842,7 @@
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="8" t="s">
         <v>26</v>
       </c>
     </row>
@@ -848,7 +850,7 @@
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -856,7 +858,7 @@
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="8" t="s">
         <v>28</v>
       </c>
     </row>

--- a/backend/State of the Market Report - Nov 2023.xlsx
+++ b/backend/State of the Market Report - Nov 2023.xlsx
@@ -17,10 +17,10 @@
     <t>Indicator</t>
   </si>
   <si>
-    <t>Current Period</t>
-  </si>
-  <si>
-    <t>Prior Period</t>
+    <t>Current Period (CP)</t>
+  </si>
+  <si>
+    <t>Prior Period (PP)</t>
   </si>
   <si>
     <t>CP Value</t>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -161,7 +161,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -506,7 +509,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" style="1" customWidth="1"/>
-    <col min="2" max="3" width="13" style="2" customWidth="1"/>
+    <col min="2" max="3" width="16" style="2" customWidth="1"/>
     <col min="4" max="5" width="10" style="3" customWidth="1"/>
     <col min="6" max="6" width="9" style="4" customWidth="1"/>
   </cols>
@@ -762,103 +765,103 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="30" style="1" customWidth="1"/>
-    <col min="2" max="2" width="100" style="8" customWidth="1"/>
+    <col min="1" max="1" width="30" style="8" customWidth="1"/>
+    <col min="2" max="2" width="100" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="9" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="9" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="9" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="9" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="9" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="9" t="s">
         <v>28</v>
       </c>
     </row>
